--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085697</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085709</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219962</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085753</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635207</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120655336</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133676553</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120673021</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2022,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563845</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54014137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79351227</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,8 +2372,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79351235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1351,55 +1351,68 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120635207</v>
+        <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Lissjön, Lissjön, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517741</v>
+        <v>517718</v>
       </c>
       <c r="R8" t="n">
-        <v>6535926</v>
+        <v>6538618</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,22 +1436,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,31 +1460,30 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635207</t>
+          <t>https://artportalen.se/Sighting/135861195</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120655336</v>
+        <v>120635207</v>
       </c>
       <c r="B9" t="n">
         <v>93235</v>
@@ -1513,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517761</v>
+        <v>517741</v>
       </c>
       <c r="R9" t="n">
-        <v>6535805</v>
+        <v>6535926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,12 +1555,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,66 +1597,61 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120655336</t>
+          <t>https://artportalen.se/Sighting/120635207</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133676553</v>
+        <v>120655336</v>
       </c>
       <c r="B10" t="n">
-        <v>58349</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Molången, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517627</v>
+        <v>517761</v>
       </c>
       <c r="R10" t="n">
-        <v>6535041</v>
+        <v>6535805</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,22 +1675,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,33 +1689,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133676553</t>
+          <t>https://artportalen.se/Sighting/120655336</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120673018</v>
+        <v>133676553</v>
       </c>
       <c r="B11" t="n">
-        <v>8444</v>
+        <v>58349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,30 +1724,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1749,13 +1760,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517611</v>
+        <v>517627</v>
       </c>
       <c r="R11" t="n">
-        <v>6534767</v>
+        <v>6535041</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,12 +1790,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,34 +1814,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120673018</t>
+          <t>https://artportalen.se/Sighting/133676553</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120673021</v>
+        <v>120673018</v>
       </c>
       <c r="B12" t="n">
-        <v>97983</v>
+        <v>8444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,31 +1848,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1860,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517608</v>
+        <v>517611</v>
       </c>
       <c r="R12" t="n">
-        <v>6534768</v>
+        <v>6534767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,16 +1943,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120673021</t>
+          <t>https://artportalen.se/Sighting/120673018</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80563845</v>
+        <v>120673021</v>
       </c>
       <c r="B13" t="n">
-        <v>93193</v>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,34 +1960,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Molången, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518322</v>
+        <v>517608</v>
       </c>
       <c r="R13" t="n">
-        <v>6533558</v>
+        <v>6534768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,12 +2022,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,33 +2036,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563845</t>
+          <t>https://artportalen.se/Sighting/120673021</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54014137</v>
+        <v>80563845</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>93193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,34 +2071,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>4363</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518326</v>
+        <v>518322</v>
       </c>
       <c r="R14" t="n">
-        <v>6533577</v>
+        <v>6533558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,12 +2125,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,27 +2145,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54014137</t>
+          <t>https://artportalen.se/Sighting/80563845</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79351227</v>
+        <v>54014137</v>
       </c>
       <c r="B15" t="n">
-        <v>58327</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,46 +2173,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518370</v>
+        <v>518326</v>
       </c>
       <c r="R15" t="n">
-        <v>6533440</v>
+        <v>6533577</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2209,22 +2227,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-04-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-04-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,24 +2247,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79351227</t>
+          <t>https://artportalen.se/Sighting/54014137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79351235</v>
+        <v>79351227</v>
       </c>
       <c r="B16" t="n">
         <v>58327</v>
@@ -2303,10 +2311,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518360</v>
+        <v>518370</v>
       </c>
       <c r="R16" t="n">
-        <v>6533430</v>
+        <v>6533440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,6 +2381,130 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79351227</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>79351235</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Baggesand, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>518360</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6533430</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-04-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-04-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/79351235</t>
         </is>
@@ -2395,6 +2527,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -1354,7 +1354,7 @@
         <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -1354,7 +1354,7 @@
         <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -1354,7 +1354,7 @@
         <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>57855</v>
+        <v>57859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -1354,7 +1354,7 @@
         <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -1354,7 +1354,7 @@
         <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>57860</v>
+        <v>57865</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 210-2024 artfynd.xlsx
+++ b/artfynd/S 210-2024 artfynd.xlsx
@@ -1354,7 +1354,7 @@
         <v>135861195</v>
       </c>
       <c r="B8" t="n">
-        <v>57865</v>
+        <v>57878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
